--- a/medical_surveys_questionnaires/047_neuro_rehabilitation_assessment_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/047_neuro_rehabilitation_assessment_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_information</t>
+          <t>patient_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Information</t>
+          <t>Patient Info</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -570,15 +570,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_info</t>
+          <t>patient_info_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Patient Info</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Patient Info 2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select a patient from the list</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,24 +592,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_info</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Patient Info</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Please select a patient from the list</t>
-        </is>
-      </c>
+          <t>Medical History</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -620,15 +620,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>rehabilitation_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Rehabilitation Goals</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter your goals</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -643,17 +647,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>physical_therapy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Physical Therapy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Please fill out medical history</t>
+          <t>Enter physical therapy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -665,20 +669,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>neurological_status</t>
+          <t>occupational_therapy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Neurological Status</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Occupational Therapy</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter occupational therapy</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -688,22 +696,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neurological_status</t>
+          <t>cognitive_therapy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Neurological Status</t>
+          <t>Cognitive Therapy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Please select neurological status</t>
+          <t>Enter cognitive therapy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -720,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rehabilitation_goals</t>
+          <t>recreational_activities</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rehabilitation Goals</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Recreational Activities</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter recreational activities</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -743,17 +755,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rehabilitation_goals</t>
+          <t>social_interactions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rehabilitation Goals</t>
+          <t>Social Interactions</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Please enter your goals</t>
+          <t>Enter social interactions</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -770,15 +782,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>physical_therapy</t>
+          <t>neurological_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Neurological Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter neurological status</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -793,17 +809,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>physical_therapy</t>
+          <t>overall_progress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Physical Therapy</t>
+          <t>Overall Progress</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enter physical therapy</t>
+          <t>Rate your overall progress</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -815,20 +831,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>occupational_therapy</t>
+          <t>progress_tracking</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Occupational Therapy</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Progress Tracking</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Track your progress</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -843,17 +863,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>occupational_therapy</t>
+          <t>goal_setting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Occupational Therapy</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Enter occupational therapy</t>
+          <t>Set specific goals</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -870,266 +890,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>speech_therapy</t>
+          <t>self_assessment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Speech Therapy</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Self-Assessment</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rate your emotions, pain levels, or energy levels</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>speech_therapy</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Speech Therapy</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Enter speech therapy</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>cognitive_therapy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Cognitive Therapy</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>cognitive_therapy</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Cognitive Therapy</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter cognitive therapy</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>recreational_activities</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Recreational Activities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>recreational_activities</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Recreational Activities</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter recreational activities</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>social_interactions</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Social Interactions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>social_interactions</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Social Interactions</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter social interactions</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>medical_history</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_history</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Enter medical history</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>neurological_status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Neurological Status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1146,12 +920,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1174,136 +948,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>patient_info_choices</t>
+          <t>patient_info_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'select_a_patient_from_the_list',_'value':_1}</t>
+          <t>select_a_patient_from_the_list</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Select a patient from the list', 'value': 1}</t>
+          <t>Select a patient from the list</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>patient_info_choices</t>
+          <t>patient_info_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'select_another_patient_from_the_list',_'value':_2}</t>
+          <t>select_another_patient_from_the_list</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Select another patient from the list', 'value': 2}</t>
+          <t>Select another patient from the list</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_info_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'select_a_patient_from_the_list',_'value':_1}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Select a patient from the list', 'value': 1}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_info_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'select_another_patient_from_the_list',_'value':_2}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Select another patient from the list', 'value': 2}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>neurological_status_choices</t>
+          <t>progress_tracking_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'select_one_option',_'value':_1}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Select one option', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>neurological_status_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'label':_'select_another_option',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'label': 'Select another option', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>neurological_status_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_'select_one_option',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': 'Select one option', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>neurological_status_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_'select_another_option',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': 'Select another option', 'value': 2}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
